--- a/Result/profitability/3073.xlsx
+++ b/Result/profitability/3073.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>0.23125</v>
+        <v>0.001250000000000008</v>
       </c>
       <c r="N2" t="n">
-        <v>37.23500000000001</v>
+        <v>34.41625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07125000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="N3" t="n">
-        <v>32.60875</v>
+        <v>25.8775</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>0.20125</v>
+        <v>0.07375000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>24.4075</v>
+        <v>21.4</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.98</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01625000000000001</v>
+        <v>-0.03124999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>19.6425</v>
+        <v>15.84</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03999999999999999</v>
+        <v>0.05250000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>14.49875</v>
+        <v>15.18875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="N7" t="n">
-        <v>13.47</v>
+        <v>12.82125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19875</v>
+        <v>0.16625</v>
       </c>
       <c r="N8" t="n">
-        <v>11.28875</v>
+        <v>12.71875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>-0.54</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01375000000000003</v>
+        <v>-0.01374999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>10.785</v>
@@ -9826,6 +9826,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3073</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>27</v>
+      </c>
+      <c r="D75" t="n">
+        <v>20</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-33.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.04875000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>-inf</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.89937106918239</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-30.42</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5573470135580798</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
